--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T16:33:35+00:00</t>
+    <t>2025-04-24T12:56:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1789,17 +1789,17 @@
   <dimension ref="A1:AN66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="59.5625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="30.06640625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.24609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.06640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="25.77734375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.9296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="254.671875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="218.3359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1808,26 +1808,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="17.79296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="101.54296875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="15.25390625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="87.0546875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="85.02734375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="185.94140625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="51.59765625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="72.89453125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="159.4140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="44.234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5102,7 +5102,7 @@
         <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>118</v>
@@ -5328,7 +5328,7 @@
         <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>101</v>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:56:51+00:00</t>
+    <t>2025-04-24T12:57:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T12:57:11+00:00</t>
+    <t>2025-04-24T13:09:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T13:09:23+00:00</t>
+    <t>2025-04-29T14:26:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T14:28:01+00:00</t>
+    <t>2026-03-04T14:06:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:06:01+00:00</t>
+    <t>2026-03-04T14:38:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T14:38:02+00:00</t>
+    <t>2026-03-04T16:46:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$64</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2402" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="454">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T16:46:41+00:00</t>
+    <t>2026-05-06T07:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -240,13 +240,13 @@
     <t>Mapping: Spécification métier vers le profil PDSm_SubmissionSetComprehensive</t>
   </si>
   <si>
+    <t>Mapping: XDS and MHD Mapping</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: XDS and MHD Mapping</t>
   </si>
   <si>
     <t>Collection
@@ -279,10 +279,10 @@
     <t>LotDeSoumission</t>
   </si>
   <si>
+    <t>XDS SubmissionSet: Used in the context of the IHE MHD ImplementationGuide</t>
+  </si>
+  <si>
     <t>Act[classCode&lt;ORG,moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>XDS SubmissionSet</t>
   </si>
   <si>
     <t>List.id</t>
@@ -443,7 +443,7 @@
     <t>List.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -484,7 +484,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -508,7 +508,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -551,7 +551,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -707,20 +707,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J03-XdsContentTypeCode-CISIS/FHIR/JDV-J03-XdsContentTypeCode-CISIS</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>List.extension:designationType.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
   </si>
   <si>
     <t>List.extension:sourceId</t>
@@ -838,13 +825,13 @@
 </t>
   </si>
   <si>
+    <t>SubmissionSet.entryUUID and SubmissionSet.uniqueId</t>
+  </si>
+  <si>
     <t>.id</t>
   </si>
   <si>
     <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>SubmissionSet.entryUUID and SubmissionSet.uniqueId</t>
   </si>
   <si>
     <t>List.identifier:uniqueId</t>
@@ -860,13 +847,7 @@
     <t>IdUnique : Identifiant unique global affecté à ce lot de soumission par son créateur. Cet attribut est utilisé à des fins de références externes alors que idLotSoumission est destiné à des fins de gestion interne.</t>
   </si>
   <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
-  </si>
-  <si>
     <t>idUnique : [0..1] Identifiant</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>List.identifier:entryUUID</t>
@@ -909,15 +890,15 @@
     <t>http://hl7.org/fhir/ValueSet/list-status|4.0.1</t>
   </si>
   <si>
+    <t>SubmissionSet.availabilityStatus</t>
+  </si>
+  <si>
     <t>.status[current=active;retired=obsolete;entered-in-error=nullified]</t>
   </si>
   <si>
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>SubmissionSet.availabilityStatus</t>
-  </si>
-  <si>
     <t>List.mode</t>
   </si>
   <si>
@@ -942,15 +923,15 @@
     <t>http://hl7.org/fhir/ValueSet/list-mode|4.0.1</t>
   </si>
   <si>
+    <t>shall be 'working'</t>
+  </si>
+  <si>
     <t>.outBoundRelationship[typeCode=COMP].target[classCode=OBS"].value</t>
   </si>
   <si>
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>shall be 'working'</t>
-  </si>
-  <si>
     <t>List.title</t>
   </si>
   <si>
@@ -969,10 +950,10 @@
     <t>titre : [0..1] Texte</t>
   </si>
   <si>
+    <t>SubmissionSet.title</t>
+  </si>
+  <si>
     <t>.title</t>
-  </si>
-  <si>
-    <t>SubmissionSet.title</t>
   </si>
   <si>
     <t>List.code</t>
@@ -1001,13 +982,13 @@
     <t>https://profiles.ihe.net/ITI/MHD/ValueSet/MHDlistTypesVS</t>
   </si>
   <si>
+    <t>shall be 'submissionset'</t>
+  </si>
+  <si>
     <t>.code</t>
   </si>
   <si>
     <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>shall be 'submissionset'</t>
   </si>
   <si>
     <t>List.subject</t>
@@ -1032,19 +1013,19 @@
     <t>idPatient : [0..1] Identifiant</t>
   </si>
   <si>
+    <t>SubmissionSet.patientId</t>
+  </si>
+  <si>
     <t>.participation[typeCode&lt;SUB].role (and sometimes .player)</t>
   </si>
   <si>
     <t>FiveWs.subject</t>
   </si>
   <si>
-    <t>SubmissionSet.patientId</t>
-  </si>
-  <si>
     <t>List.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1082,13 +1063,13 @@
     <t>dateSoumission : [1..1] DateHeure</t>
   </si>
   <si>
+    <t>SubmissionSet.submissionTime</t>
+  </si>
+  <si>
     <t>.participation[typeCode&lt;AUT].time[type=TS]</t>
   </si>
   <si>
     <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>SubmissionSet.submissionTime</t>
   </si>
   <si>
     <t>List.source</t>
@@ -1114,13 +1095,13 @@
     <t>Allows follow-up as well as context.</t>
   </si>
   <si>
+    <t>SubmissionSet.author</t>
+  </si>
+  <si>
     <t>.participation[typeCode&lt;AUT].role[classCode=REL].player[classCode=PSN,determinerCode=INST] or .participation[typeCode&lt;AUT].role[classCode=REL].player[classCode=DEV,determinerCode=INST]</t>
   </si>
   <si>
     <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>SubmissionSet.author</t>
   </si>
   <si>
     <t>List.source.id</t>
@@ -1179,16 +1160,6 @@
 </t>
   </si>
   <si>
-    <t>List.source.extension:authorOrg.value[x]:valueReference</t>
-  </si>
-  <si>
-    <t>valueReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference
-</t>
-  </si>
-  <si>
     <t>List.source.reference</t>
   </si>
   <si>
@@ -1224,7 +1195,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1284,7 +1255,7 @@
     <t>What order applies to the items in a list.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order</t>
+    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
@@ -1306,10 +1277,10 @@
     <t>commentaire : [0..1] Texte</t>
   </si>
   <si>
+    <t>SubmissionSet.comments</t>
+  </si>
+  <si>
     <t>.inboundRelationship[typeCode=SUBJ].act.text</t>
-  </si>
-  <si>
-    <t>SubmissionSet.comments</t>
   </si>
   <si>
     <t>List.entry</t>
@@ -1379,7 +1350,7 @@
     <t>Codes that provide further information about the reason and meaning of the item in the list.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-item-flag</t>
+    <t>http://hl7.org/fhir/ValueSet/list-item-flag|4.0.1</t>
   </si>
   <si>
     <t>List.entry.deleted</t>
@@ -1442,12 +1413,12 @@
     <t>Classeur : [0..*]</t>
   </si>
   <si>
+    <t>references to DocumentReference(s) and Folder List(s)</t>
+  </si>
+  <si>
     <t>.target or .role or .role.entity</t>
   </si>
   <si>
-    <t>references to DocumentReference(s) and Folder List(s)</t>
-  </si>
-  <si>
     <t>List.emptyReason</t>
   </si>
   <si>
@@ -1466,7 +1437,7 @@
     <t>If a list is empty, why it is empty.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
@@ -1786,10 +1757,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN66"/>
+  <dimension ref="A1:AN64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.06640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.5859375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="25.77734375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="19.9296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1825,9 +1796,9 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="72.89453125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="159.4140625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="44.234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="62.75390625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="159.4140625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2058,10 +2029,10 @@
         <v>86</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" hidden="true">
@@ -2393,10 +2364,10 @@
         <v>80</v>
       </c>
       <c r="AL5" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM5" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="AM5" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>80</v>
@@ -2507,10 +2478,10 @@
         <v>80</v>
       </c>
       <c r="AL6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM6" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="AM6" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>80</v>
@@ -2963,13 +2934,13 @@
         <v>80</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>142</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" hidden="true">
@@ -3533,10 +3504,10 @@
         <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>80</v>
@@ -3647,10 +3618,10 @@
         <v>80</v>
       </c>
       <c r="AL16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>80</v>
@@ -3983,10 +3954,10 @@
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>80</v>
@@ -4209,10 +4180,10 @@
         <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>80</v>
@@ -4289,17 +4260,19 @@
         <v>80</v>
       </c>
       <c r="AB22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AC22" s="2"/>
-      <c r="AD22" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4317,10 +4290,10 @@
         <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>80</v>
@@ -4328,13 +4301,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>80</v>
@@ -4356,13 +4329,13 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4413,25 +4386,25 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>80</v>
+        <v>226</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>189</v>
+        <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>80</v>
@@ -4442,23 +4415,23 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4470,13 +4443,13 @@
         <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4542,10 +4515,10 @@
         <v>118</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>80</v>
+        <v>232</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>80</v>
@@ -4556,13 +4529,13 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>80</v>
@@ -4572,7 +4545,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
@@ -4584,13 +4557,13 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4656,7 +4629,7 @@
         <v>118</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>80</v>
+        <v>238</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>80</v>
@@ -4665,18 +4638,18 @@
         <v>80</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>236</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>80</v>
@@ -4686,10 +4659,10 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>80</v>
@@ -4698,13 +4671,13 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4770,7 +4743,7 @@
         <v>118</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>242</v>
+        <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>80</v>
@@ -4782,16 +4755,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>80</v>
       </c>
@@ -4800,10 +4771,10 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>80</v>
@@ -4812,13 +4783,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>245</v>
+        <v>103</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>247</v>
+        <v>105</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4869,19 +4840,19 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>194</v>
+        <v>106</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
@@ -4890,7 +4861,7 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -4898,10 +4869,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4912,7 +4883,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -4924,13 +4895,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>104</v>
+        <v>192</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4969,37 +4940,37 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>80</v>
@@ -5010,10 +4981,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5021,10 +4992,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>80</v>
@@ -5036,22 +5007,24 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>80</v>
@@ -5081,31 +5054,31 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>117</v>
+        <v>213</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -5114,7 +5087,7 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -5122,10 +5095,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5133,7 +5106,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>89</v>
@@ -5148,24 +5121,22 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>131</v>
+        <v>249</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>80</v>
@@ -5207,10 +5178,10 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>89</v>
@@ -5219,16 +5190,16 @@
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -5236,10 +5207,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>215</v>
+        <v>250</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5250,25 +5221,25 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>253</v>
+        <v>110</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5319,25 +5290,25 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>189</v>
+        <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
@@ -5348,10 +5319,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5362,25 +5333,25 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>253</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>192</v>
+        <v>254</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>193</v>
+        <v>255</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5419,19 +5390,17 @@
         <v>80</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="AC32" s="2"/>
       <c r="AD32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5443,29 +5412,31 @@
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>80</v>
+        <v>259</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="D33" t="s" s="2">
         <v>80</v>
       </c>
@@ -5474,10 +5445,10 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>80</v>
@@ -5486,13 +5457,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5531,17 +5502,19 @@
         <v>80</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5556,27 +5529,27 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>80</v>
+        <v>264</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>80</v>
@@ -5586,7 +5559,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>90</v>
@@ -5598,13 +5571,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5655,7 +5628,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5664,7 +5637,7 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>101</v>
@@ -5673,54 +5646,54 @@
         <v>269</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>80</v>
+        <v>259</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>90</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -5730,7 +5703,7 @@
         <v>80</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>80</v>
+        <v>274</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>80</v>
@@ -5745,13 +5718,13 @@
         <v>80</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>80</v>
+        <v>275</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>80</v>
+        <v>277</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>80</v>
@@ -5769,39 +5742,39 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>275</v>
+        <v>238</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>80</v>
+        <v>279</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>80</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5827,15 +5800,17 @@
         <v>166</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5844,7 +5819,7 @@
         <v>80</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>80</v>
@@ -5859,31 +5834,31 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>89</v>
@@ -5898,24 +5873,24 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>242</v>
+        <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5923,7 +5898,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>89</v>
@@ -5932,25 +5907,23 @@
         <v>90</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -5960,49 +5933,49 @@
         <v>80</v>
       </c>
       <c r="S37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="T37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>287</v>
-      </c>
       <c r="AG37" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>89</v>
@@ -6014,24 +5987,24 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>80</v>
+        <v>297</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>297</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6039,7 +6012,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>89</v>
@@ -6054,17 +6027,19 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>216</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="O38" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6074,10 +6049,10 @@
         <v>80</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>80</v>
+        <v>305</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>302</v>
+        <v>80</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>80</v>
@@ -6089,13 +6064,11 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>80</v>
+        <v>306</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6113,7 +6086,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6128,24 +6101,24 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>303</v>
+        <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>80</v>
+        <v>308</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6168,19 +6141,19 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>216</v>
+        <v>311</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -6190,7 +6163,7 @@
         <v>80</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>311</v>
+        <v>80</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>80</v>
@@ -6205,11 +6178,13 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>312</v>
+        <v>80</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -6227,7 +6202,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6242,24 +6217,24 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>80</v>
+        <v>316</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6267,35 +6242,31 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
       </c>
@@ -6343,7 +6314,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6358,10 +6329,10 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>322</v>
+        <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>323</v>
+        <v>107</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>324</v>
@@ -6370,7 +6341,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>326</v>
       </c>
@@ -6383,19 +6354,19 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
         <v>327</v>
@@ -6406,8 +6377,12 @@
       <c r="M41" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+      <c r="N41" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
       </c>
@@ -6470,28 +6445,28 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>107</v>
+        <v>335</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>80</v>
+        <v>337</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6510,19 +6485,19 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -6571,7 +6546,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6586,60 +6561,56 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>338</v>
+        <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>343</v>
+        <v>80</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>344</v>
+        <v>103</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>345</v>
+        <v>104</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
@@ -6687,7 +6658,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>342</v>
+        <v>106</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6699,38 +6670,38 @@
         <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>349</v>
+        <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>350</v>
+        <v>107</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>351</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>80</v>
@@ -6742,15 +6713,17 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -6787,40 +6760,40 @@
         <v>80</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>80</v>
@@ -6828,21 +6801,23 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="D45" t="s" s="2">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -6854,17 +6829,15 @@
         <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>110</v>
+        <v>350</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>111</v>
+        <v>351</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -6901,16 +6874,16 @@
         <v>80</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>117</v>
@@ -6928,10 +6901,10 @@
         <v>118</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>80</v>
@@ -6945,11 +6918,9 @@
         <v>354</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="C46" t="s" s="2">
         <v>355</v>
       </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>80</v>
       </c>
@@ -6970,13 +6941,13 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>356</v>
+        <v>103</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>357</v>
+        <v>104</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>358</v>
+        <v>105</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7027,28 +6998,28 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>359</v>
+        <v>80</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7056,10 +7027,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7070,7 +7041,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>80</v>
@@ -7082,13 +7053,13 @@
         <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>104</v>
+        <v>192</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7127,37 +7098,37 @@
         <v>80</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
@@ -7168,10 +7139,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7179,10 +7150,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>80</v>
@@ -7194,22 +7165,24 @@
         <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>80</v>
+        <v>360</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>80</v>
@@ -7239,31 +7212,31 @@
         <v>80</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>117</v>
+        <v>213</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>80</v>
@@ -7272,7 +7245,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7280,10 +7253,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7306,24 +7279,22 @@
         <v>80</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>131</v>
+        <v>363</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>80</v>
@@ -7365,10 +7336,10 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>89</v>
@@ -7377,16 +7348,16 @@
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -7394,10 +7365,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7405,7 +7376,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>89</v>
@@ -7417,18 +7388,20 @@
         <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>369</v>
+        <v>103</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>217</v>
+        <v>365</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -7465,17 +7438,19 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AC50" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="AD50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>221</v>
+        <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>222</v>
+        <v>368</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7484,7 +7459,7 @@
         <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>80</v>
+        <v>369</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>101</v>
@@ -7493,10 +7468,10 @@
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
@@ -7507,17 +7482,15 @@
         <v>370</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>89</v>
@@ -7529,18 +7502,20 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L51" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N51" s="2"/>
+      <c r="N51" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7565,13 +7540,13 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>80</v>
+        <v>374</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>80</v>
+        <v>375</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -7589,7 +7564,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>222</v>
+        <v>376</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7607,10 +7582,10 @@
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -7618,10 +7593,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7644,16 +7619,16 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>103</v>
+        <v>253</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7703,7 +7678,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7712,7 +7687,7 @@
         <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>378</v>
+        <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>101</v>
@@ -7721,10 +7696,10 @@
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>189</v>
+        <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>80</v>
+        <v>382</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -7732,10 +7707,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7758,16 +7733,16 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7793,13 +7768,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>383</v>
+        <v>80</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>384</v>
+        <v>80</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -7817,7 +7792,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7835,10 +7810,10 @@
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -7846,10 +7821,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7860,7 +7835,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>80</v>
@@ -7869,21 +7844,23 @@
         <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>257</v>
+        <v>216</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -7907,13 +7884,13 @@
         <v>80</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>80</v>
+        <v>393</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>80</v>
+        <v>394</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>80</v>
@@ -7931,7 +7908,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7949,10 +7926,10 @@
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>391</v>
+        <v>107</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>80</v>
+        <v>395</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -7960,10 +7937,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7983,20 +7960,18 @@
         <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>103</v>
+        <v>397</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -8051,7 +8026,7 @@
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>80</v>
@@ -8060,13 +8035,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>189</v>
+        <v>401</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>80</v>
+        <v>402</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
@@ -8074,10 +8049,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8088,7 +8063,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>80</v>
@@ -8100,20 +8075,18 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>216</v>
+        <v>404</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8137,40 +8110,40 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>402</v>
+        <v>80</v>
       </c>
       <c r="Z56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AA56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>397</v>
-      </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>80</v>
+        <v>408</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>101</v>
@@ -8179,21 +8152,21 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>404</v>
+        <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>80</v>
+        <v>409</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>107</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8216,13 +8189,13 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>406</v>
+        <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>407</v>
+        <v>104</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>408</v>
+        <v>105</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8273,43 +8246,43 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>405</v>
+        <v>106</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>409</v>
+        <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>411</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8328,16 +8301,16 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>413</v>
+        <v>110</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>414</v>
+        <v>111</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>415</v>
+        <v>112</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>416</v>
+        <v>113</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8387,7 +8360,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>412</v>
+        <v>117</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8396,19 +8369,19 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>417</v>
+        <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>418</v>
+        <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
@@ -8416,42 +8389,46 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>80</v>
+        <v>413</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>104</v>
+        <v>414</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -8499,28 +8476,28 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>106</v>
+        <v>417</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -8528,21 +8505,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>80</v>
@@ -8554,18 +8531,20 @@
         <v>80</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>110</v>
+        <v>216</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>111</v>
+        <v>419</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>112</v>
+        <v>420</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
       </c>
@@ -8589,13 +8568,13 @@
         <v>80</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>80</v>
+        <v>423</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>80</v>
+        <v>424</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>80</v>
@@ -8613,19 +8592,19 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>117</v>
+        <v>418</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>80</v>
@@ -8634,7 +8613,7 @@
         <v>107</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>80</v>
+        <v>290</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>80</v>
@@ -8642,21 +8621,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>422</v>
+        <v>80</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>80</v>
@@ -8665,92 +8644,94 @@
         <v>90</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>110</v>
+        <v>426</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>113</v>
+        <v>429</v>
       </c>
       <c r="O61" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q61" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="R61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="P61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>426</v>
-      </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>80</v>
+        <v>432</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>189</v>
+        <v>107</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>80</v>
+        <v>433</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>80</v>
@@ -8758,10 +8739,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8784,19 +8765,17 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>216</v>
+        <v>327</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>80</v>
@@ -8821,13 +8800,13 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>432</v>
+        <v>80</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>433</v>
+        <v>80</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -8845,7 +8824,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8863,21 +8842,21 @@
         <v>80</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>295</v>
+        <v>107</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>80</v>
+        <v>438</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>107</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8885,117 +8864,111 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O63" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="P63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q63" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="R63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>434</v>
-      </c>
       <c r="AG63" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>441</v>
+        <v>80</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>80</v>
+        <v>443</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>80</v>
+        <v>445</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>107</v>
+        <v>80</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9018,17 +8991,19 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>333</v>
+        <v>216</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="O64" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -9053,13 +9028,13 @@
         <v>80</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>80</v>
+        <v>451</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>80</v>
+        <v>452</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>80</v>
@@ -9077,7 +9052,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9086,7 +9061,7 @@
         <v>89</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>80</v>
+        <v>408</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>101</v>
@@ -9095,245 +9070,17 @@
         <v>80</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>447</v>
+        <v>107</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>80</v>
+        <v>453</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
-      <c r="P65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>107</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN66">
+  <autoFilter ref="A1:AN64">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9343,7 +9090,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI65">
+  <conditionalFormatting sqref="A2:AI63">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:19:11+00:00</t>
+    <t>2026-05-27T14:14:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:14:06+00:00</t>
+    <t>2026-05-28T14:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:04:20+00:00</t>
+    <t>2026-05-28T14:30:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:30:01+00:00</t>
+    <t>2026-06-03T13:49:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T13:49:29+00:00</t>
+    <t>2026-06-03T13:50:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T13:50:50+00:00</t>
+    <t>2026-06-30T13:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:26:19+00:00</t>
+    <t>2026-06-30T13:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:34:41+00:00</t>
+    <t>2026-06-30T16:19:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T16:19:40+00:00</t>
+    <t>2026-07-15T16:15:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T16:15:50+00:00</t>
+    <t>2026-07-27T15:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:54+00:00</t>
+    <t>2026-08-06T13:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:06:39+00:00</t>
+    <t>2026-08-06T14:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
+++ b/main/ig/StructureDefinition-pdsm-submissionset-comprehensive.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T14:18:59+00:00</t>
+    <t>2026-08-06T14:57:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
